--- a/docs/interview_matrix_analysis.xlsx
+++ b/docs/interview_matrix_analysis.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afidhu Nurudini\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afidhu Nurudini\Desktop\COMPLIANCE-RISK-AND-SAFETY-MANAGEMENT-\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5A4D2C-8F1B-4AAB-A045-5ADDFB855324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D982CB3B-D76E-47B5-BAAA-A5855699189E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interview Matrix Analysis" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -46,21 +57,12 @@
     <t>Current Role</t>
   </si>
   <si>
-    <t>Supervises building operations and compliance</t>
-  </si>
-  <si>
     <t>Repairs facility equipment</t>
   </si>
   <si>
     <t>Monitors safety and compliance</t>
   </si>
   <si>
-    <t>Oversees workplace safety and compliance</t>
-  </si>
-  <si>
-    <t>Supports daily facility operations</t>
-  </si>
-  <si>
     <t>Different stakeholders participate in facility compliance management</t>
   </si>
   <si>
@@ -272,6 +274,15 @@
   </si>
   <si>
     <t>Electrical systems, lifts,pressure vessels, boilers</t>
+  </si>
+  <si>
+    <t>Supervises building operations and assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversees workplace safety </t>
+  </si>
+  <si>
+    <t>use facility</t>
   </si>
 </sst>
 </file>
@@ -617,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -652,275 +663,281 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G7" t="s">
         <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" t="s">
+      <c r="G8" t="s">
         <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s">
+      <c r="G9" t="s">
         <v>53</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>59</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
         <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
         <v>65</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>66</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G11" t="s">
         <v>67</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
         <v>71</v>
       </c>
-      <c r="B12" t="s">
+      <c r="G12" t="s">
         <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
         <v>77</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
         <v>78</v>
       </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
         <v>79</v>
       </c>
-      <c r="E13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" t="s">
-        <v>82</v>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f>+E17</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
